--- a/public/exports/19583910.xlsx
+++ b/public/exports/19583910.xlsx
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">717694, 2154187</t>
+          <t xml:space="preserve">233605, 233616, 233627</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F9">
-        <v>562</v>
+        <v>4938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,30 +481,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150843</t>
+          <t xml:space="preserve">717694, 2154187</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F10">
-        <v>748</v>
+        <v>562</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013280</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-05</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -531,25 +531,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858810</t>
+          <t xml:space="preserve">2150843</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>2296</v>
+        <v>748</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057986</t>
+          <t xml:space="preserve">200013280</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-08</t>
+          <t xml:space="preserve">2019-05-05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152868</t>
+          <t xml:space="preserve">2152871</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F13">
-        <v>456</v>
+        <v>718</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255988</t>
+          <t xml:space="preserve">311264252</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -681,25 +681,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152868</t>
+          <t xml:space="preserve">8858793</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>404</v>
+        <v>1143</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255988</t>
+          <t xml:space="preserve">311264256</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -731,20 +731,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152868</t>
+          <t xml:space="preserve">8858793</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F15">
-        <v>622</v>
+        <v>258</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264253</t>
+          <t xml:space="preserve">311264255</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152871</t>
+          <t xml:space="preserve">8858789</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>718</v>
+        <v>518</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264252</t>
+          <t xml:space="preserve">311285642</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2027-11-24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858793</t>
+          <t xml:space="preserve">2152868</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="F17">
-        <v>1143</v>
+        <v>456</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264256</t>
+          <t xml:space="preserve">311289960</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858793</t>
+          <t xml:space="preserve">2152868</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264255</t>
+          <t xml:space="preserve">311289960</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858810</t>
+          <t xml:space="preserve">2152868</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F19">
-        <v>480</v>
+        <v>622</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282774</t>
+          <t xml:space="preserve">311289960</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-08</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -981,25 +981,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">233605, 233616, 233627</t>
+          <t xml:space="preserve">2153273</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
-        <v>4938</v>
+        <v>564</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285345</t>
+          <t xml:space="preserve">311289966</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858789</t>
+          <t xml:space="preserve">2153424</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="F21">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285642</t>
+          <t xml:space="preserve">311289968</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-24</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2153273</t>
+          <t xml:space="preserve">8858810</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="F22">
-        <v>564</v>
+        <v>2296</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289966</t>
+          <t xml:space="preserve">311289969</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2153424</t>
+          <t xml:space="preserve">8858810</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F23">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289968</t>
+          <t xml:space="preserve">311289969</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">

--- a/public/exports/19583910.xlsx
+++ b/public/exports/19583910.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:L45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Seminarievej 25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100035841</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>1245</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2151334</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2270</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2151334</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1345</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2151334</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>857</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2151334</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>907</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vallensbæk Havnevej 20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2154187</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>530</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vallensbæk Havnevej 18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2154187</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>575</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vallensbæk Stationstorv 6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">233605, 233616, 233627</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>4938</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krabben 7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">717694, 2154187</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>562</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mejsebo 2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2150843</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>748</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">200013280</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-05-05</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsparken 57</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">100039101</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1240</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">311255989</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løkkekrogen 11G</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2152871</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>718</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">311264252</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsparken 80</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858793</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1143</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311264256</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammelgårds Alle 37</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858793</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>258</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311264255</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højrupgårdsvej 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858789</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>518</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311285642</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311285644</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-24</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løkkekrogen 11E</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2152868</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>456</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311289960</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løkkekrogen 11D</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2152868</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>404</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311289960</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løkkekrogen 11A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2152868</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>622</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311289960</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbækvej 5A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153273</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>564</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311289966</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tværbækvej 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153424</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>504</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311289968</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsvej 125</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858810</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>2296</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311289969</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsvej 123</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858810</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>480</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311289969</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Syvhøjvænge 163</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153694</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>951</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311297027</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-09</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hasselbo 24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2150845</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1033</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311298047</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-16</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gymnasievej 21</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">8231359</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1100</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311317056</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-05-29</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gymnasievej 19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">8231359</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>1617</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311317056</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-05-29</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbækvej 5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153273</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>623</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311318745</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-06</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsvej 121</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858810</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>1615</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311319065</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsparken 78</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858793</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>428</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311322723</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsparken 76</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858793</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>465</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311322723</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vejlegårdsparken 76</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858793</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>453</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311322723</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vallensbæk Stationstorv 40</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858893</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>1689</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311322726</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858806</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>850</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311323593</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858794</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>1591</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311323824</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-29</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858794</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>5696</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311325902</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-30</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højstruphave 10</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">100013332</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>2944</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311325914</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-07-11</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gymnasievej 37</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">8506485</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>2883</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311326602</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-07-16</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 19</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153297</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>11200</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311326979</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-07-18</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 17</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2153297</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1448</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311326979</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-07-18</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vallensbæk Stationstorv 100</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2665</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858893</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>9275</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311327603</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-07-24</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsbred 197</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858892</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>13436</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311328785</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-08-02</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsbred 197</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">8858892</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>4427</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311328785</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-08-02</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Løkkekrogen 11B</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2152868</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>814</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311453425</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,39 +2671,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Idræts Alle 17</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2625</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">100778138</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>1141</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311850559</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:L45"/>
 </worksheet>
 </file>
--- a/public/exports/19583910.xlsx
+++ b/public/exports/19583910.xlsx
@@ -86,31 +86,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153</t>
+          <t xml:space="preserve">187</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seminarievej 25</t>
+          <t xml:space="preserve">Idræts Alle 5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2625</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035841</t>
+          <t xml:space="preserve">2151334</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>1245</v>
+        <v>2270</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -166,11 +166,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H3">
-        <v>2270</v>
+        <v>1345</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H4">
-        <v>1345</v>
+        <v>857</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -286,11 +286,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H5">
-        <v>857</v>
+        <v>907</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 5</t>
+          <t xml:space="preserve">Krabben 7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2625</t>
+          <t xml:space="preserve">2665</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151334</t>
+          <t xml:space="preserve">717694, 2154187</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H6">
-        <v>907</v>
+        <v>562</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -386,31 +386,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">187</t>
+          <t xml:space="preserve">153</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vallensbæk Havnevej 20</t>
+          <t xml:space="preserve">Seminarievej 25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2665</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154187</t>
+          <t xml:space="preserve">100035841</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>530</v>
+        <v>1245</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vallensbæk Stationstorv 6</t>
+          <t xml:space="preserve">Vallensbæk Havnevej 20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">233605, 233616, 233627</t>
+          <t xml:space="preserve">2154187</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H9">
-        <v>4938</v>
+        <v>530</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krabben 7</t>
+          <t xml:space="preserve">Mejsebo 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,30 +581,30 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">717694, 2154187</t>
+          <t xml:space="preserve">2150843</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>562</v>
+        <v>748</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013280</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejsebo 2</t>
+          <t xml:space="preserve">Vejlegårdsparken 57</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2150843</t>
+          <t xml:space="preserve">100039101</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,26 +650,26 @@
         </is>
       </c>
       <c r="H11">
-        <v>748</v>
+        <v>1240</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013280</t>
+          <t xml:space="preserve">311255989</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-05</t>
+          <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlegårdsparken 57</t>
+          <t xml:space="preserve">Gammelgårds Alle 37</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,25 +701,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">100039101</t>
+          <t xml:space="preserve">8858793</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H12">
-        <v>1240</v>
+        <v>258</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255989</t>
+          <t xml:space="preserve">311264255</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgårds Alle 37</t>
+          <t xml:space="preserve">Vallensbæk Stationstorv 6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858793</t>
+          <t xml:space="preserve">233605, 233616, 233627</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H15">
-        <v>258</v>
+        <v>4938</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264255</t>
+          <t xml:space="preserve">311285345</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285644</t>
+          <t xml:space="preserve">311285642</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -991,30 +991,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løkkekrogen 11E</t>
+          <t xml:space="preserve">Lundbækvej 5A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2625</t>
+          <t xml:space="preserve">2665</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2152868</t>
+          <t xml:space="preserve">2153273</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>456</v>
+        <v>564</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289960</t>
+          <t xml:space="preserve">311289966</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løkkekrogen 11D</t>
+          <t xml:space="preserve">Løkkekrogen 11A</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1066,11 +1066,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H18">
-        <v>404</v>
+        <v>622</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løkkekrogen 11A</t>
+          <t xml:space="preserve">Løkkekrogen 11D</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H19">
-        <v>622</v>
+        <v>404</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,30 +1171,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbækvej 5A</t>
+          <t xml:space="preserve">Løkkekrogen 11E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2665</t>
+          <t xml:space="preserve">2625</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2153273</t>
+          <t xml:space="preserve">2152868</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>564</v>
+        <v>456</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289966</t>
+          <t xml:space="preserve">311289960</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlegårdsvej 125</t>
+          <t xml:space="preserve">Vejlegårdsvej 123</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1306,11 +1306,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H22">
-        <v>2296</v>
+        <v>480</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlegårdsvej 123</t>
+          <t xml:space="preserve">Vejlegårdsvej 125</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1366,11 +1366,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>480</v>
+        <v>2296</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 21</t>
+          <t xml:space="preserve">Gymnasievej 19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1546,11 +1546,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H26">
-        <v>1100</v>
+        <v>1617</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gymnasievej 19</t>
+          <t xml:space="preserve">Gymnasievej 21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>1617</v>
+        <v>1100</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlegårdsparken 78</t>
+          <t xml:space="preserve">Vallensbæk Stationstorv 40</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,20 +1781,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858793</t>
+          <t xml:space="preserve">8858893</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>428</v>
+        <v>1689</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311322723</t>
+          <t xml:space="preserve">311322726</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vallensbæk Stationstorv 40</t>
+          <t xml:space="preserve">Vejlegårdsparken 78</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858893</t>
+          <t xml:space="preserve">8858793</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H33">
-        <v>1689</v>
+        <v>428</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311322726</t>
+          <t xml:space="preserve">311322723</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 19</t>
+          <t xml:space="preserve">Egholmvej 17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2326,11 +2326,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39">
-        <v>11200</v>
+        <v>1448</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 17</t>
+          <t xml:space="preserve">Egholmvej 19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>1448</v>
+        <v>11200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>

--- a/public/exports/19583910.xlsx
+++ b/public/exports/19583910.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:M45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-05</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-24</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-09</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-16</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-29</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-29</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-06</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-25</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-28</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-29</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-30</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-11</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-16</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-18</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-18</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-07-24</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-02</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-02</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-10</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,21 +2919,26 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engko Aps</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L45"/>
+  <autoFilter ref="A1:M45"/>
 </worksheet>
 </file>